--- a/virtual_event_forms/022_virtual_event_access_renewal_form--virtual_event_forms.xlsx
+++ b/virtual_event_forms/022_virtual_event_access_renewal_form--virtual_event_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'payment_method_1',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'payment_method_1', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'online_payment_gateway',_'label':_'online_payment_gateway'}</t>
+          <t>online_payment_gateway</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'online_payment_gateway', 'label': 'Online Payment Gateway'}</t>
+          <t>Online Payment Gateway</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'offline_payment',_'label':_'offline_payment'}</t>
+          <t>offline_payment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'offline_payment', 'label': 'Offline Payment'}</t>
+          <t>Offline Payment</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'payment_method_1',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'payment_method_1', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'online_payment_gateway',_'label':_'online_payment_gateway'}</t>
+          <t>online_payment_gateway</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'online_payment_gateway', 'label': 'Online Payment Gateway'}</t>
+          <t>Online Payment Gateway</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'offline_payment',_'label':_'offline_payment'}</t>
+          <t>offline_payment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'offline_payment', 'label': 'Offline Payment'}</t>
+          <t>Offline Payment</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'payment_frequency_1',_'label':_'one_time'}</t>
+          <t>one_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'payment_frequency_1', 'label': 'One Time'}</t>
+          <t>One Time</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'payment_frequency_2',_'label':_'multiple_times'}</t>
+          <t>multiple_times</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'payment_frequency_2', 'label': 'Multiple Times'}</t>
+          <t>Multiple Times</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'event_status_1',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'event_status_1', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'event_status_2',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'event_status_2', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'payment_status_1',_'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'payment_status_1', 'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'payment_status_2',_'label':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'payment_status_2', 'label': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'event_type_1',_'label':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'event_type_1', 'label': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'event_type_2',_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'event_type_2', 'label': 'In-Person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'event_time_zone_1',_'label':_'utc'}</t>
+          <t>utc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'event_time_zone_1', 'label': 'UTC'}</t>
+          <t>UTC</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'event_time_zone_2',_'label':_'est'}</t>
+          <t>est</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'event_time_zone_2', 'label': 'EST'}</t>
+          <t>EST</t>
         </is>
       </c>
     </row>
